--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_2_10.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_2_10.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268974.3716841202</v>
+        <v>287235.7912083166</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4964010.941928674</v>
+        <v>4921297.203522781</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22285259.10284261</v>
+        <v>22243395.367831</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4042825.87678395</v>
+        <v>4061631.788980304</v>
       </c>
     </row>
     <row r="11">
@@ -1876,19 +1876,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.006138603635352</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1922,19 +1922,19 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3.259547277377497</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2052,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.006138603635353</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2113,31 +2113,31 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>35.23199999999997</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>28.88091821707973</v>
       </c>
     </row>
     <row r="21">
@@ -2147,16 +2147,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="22">
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2244,10 +2244,10 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2277,22 +2277,22 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2308,16 +2308,16 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2353,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2368,10 +2368,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2432,25 +2432,25 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S24" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>40</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2526,10 +2526,10 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X25" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2590,10 +2590,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W26" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
     </row>
     <row r="27">
@@ -2627,10 +2627,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2675,22 +2675,22 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>35.23199999999997</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="28">
@@ -2745,28 +2745,28 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>0.790450447682255</v>
       </c>
       <c r="U28" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2788,16 +2788,16 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2830,22 +2830,22 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2909,13 +2909,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2949,16 +2949,16 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2994,19 +2994,19 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
     </row>
     <row r="32">
@@ -3019,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3095,16 +3095,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -3113,10 +3113,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>38.87161743162454</v>
       </c>
       <c r="I33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3186,10 +3186,10 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -3216,19 +3216,19 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="T34" t="n">
-        <v>6.415584701379554</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3310,16 +3310,16 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X35" t="n">
-        <v>35.23199999999997</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3389,19 +3389,19 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>40</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="W36" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y36" t="n">
-        <v>35.23199999999997</v>
+        <v>44.13217237922859</v>
       </c>
     </row>
     <row r="37">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -3426,13 +3426,13 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>9.137025436486075</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3502,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3541,13 +3541,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>35.23199999999998</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>38.87161743162455</v>
       </c>
     </row>
     <row r="39">
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>40</v>
+        <v>38.87161743162455</v>
       </c>
       <c r="V39" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="W39" t="n">
-        <v>35.23199999999997</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -3654,25 +3654,25 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>9.137025436486079</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.790450447682262</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>24.87477961344436</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3784,19 +3784,19 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="42">
@@ -3809,13 +3809,13 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>35.23199999999997</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>34.86547882798917</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3857,10 +3857,10 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3869,13 +3869,13 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
     <row r="43">
@@ -3897,10 +3897,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9.977552361264268</v>
       </c>
       <c r="G43" t="n">
-        <v>9.137025436486079</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -3936,25 +3936,25 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Y43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4.684744279909647</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.684744279909647</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.684744279909647</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>9.187556743123771</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>13.69036920633789</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>14.1465770194153</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>9.552339224073879</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.958101428732459</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4.410468283527761</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.117996286176754</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.866676096605165</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>9.369488559819288</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>9.369488559819288</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>9.369488559819288</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>13.69036920633789</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>13.69036920633789</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.684744279909647</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>9.187556743123771</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>13.69036920633789</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>18.19318166955202</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>13.5989438742106</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>9.00470607886918</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.410468283527761</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.3638636333910404</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K20" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L20" t="n">
-        <v>82.40000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M20" t="n">
-        <v>82.40000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N20" t="n">
-        <v>120.4</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="O20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P20" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q20" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="R20" t="n">
-        <v>160</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="S20" t="n">
-        <v>119.5959595959596</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="T20" t="n">
-        <v>79.19191919191917</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="U20" t="n">
-        <v>38.78787878787876</v>
+        <v>166.4370741486873</v>
       </c>
       <c r="V20" t="n">
-        <v>3.2</v>
+        <v>121.8591222504766</v>
       </c>
       <c r="W20" t="n">
-        <v>3.2</v>
+        <v>77.28117035226589</v>
       </c>
       <c r="X20" t="n">
-        <v>3.2</v>
+        <v>32.70321845405519</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="C21" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="D21" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K21" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L21" t="n">
-        <v>82.40000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M21" t="n">
-        <v>122</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N21" t="n">
-        <v>160</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="O21" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q21" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R21" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S21" t="n">
-        <v>84.00808080808082</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T21" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U21" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V21" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W21" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X21" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Y21" t="n">
-        <v>43.60404040404041</v>
+        <v>131.9507376187037</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C22" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D22" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E22" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F22" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G22" t="n">
-        <v>52.83335902675362</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H22" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L22" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M22" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N22" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R22" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S22" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="T22" t="n">
-        <v>133.6414398348344</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="U22" t="n">
-        <v>133.6414398348344</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="V22" t="n">
-        <v>133.6414398348344</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="W22" t="n">
-        <v>93.23739943079403</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="X22" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y22" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>79.19191919191917</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="C23" t="n">
-        <v>79.19191919191917</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D23" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E23" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L23" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M23" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N23" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q23" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R23" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S23" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T23" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U23" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V23" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W23" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X23" t="n">
-        <v>79.19191919191917</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="Y23" t="n">
-        <v>79.19191919191917</v>
+        <v>42.79483382228227</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M24" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="N24" t="n">
-        <v>82.40000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O24" t="n">
-        <v>122</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P24" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q24" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R24" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S24" t="n">
-        <v>124.4121212121212</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T24" t="n">
-        <v>84.00808080808082</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U24" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="V24" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="W24" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="X24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="C25" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="D25" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L25" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M25" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N25" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P25" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q25" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R25" t="n">
-        <v>52.83335902675362</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S25" t="n">
-        <v>52.83335902675362</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T25" t="n">
-        <v>52.83335902675362</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U25" t="n">
-        <v>52.83335902675362</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V25" t="n">
-        <v>52.83335902675362</v>
+        <v>138.062864280609</v>
       </c>
       <c r="W25" t="n">
-        <v>52.83335902675362</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="X25" t="n">
-        <v>12.42931862271321</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="Y25" t="n">
-        <v>12.42931862271321</v>
+        <v>93.48491238239833</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K26" t="n">
-        <v>42.8</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L26" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M26" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N26" t="n">
-        <v>82.40000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O26" t="n">
-        <v>122</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q26" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R26" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S26" t="n">
-        <v>79.19191919191917</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T26" t="n">
-        <v>79.19191919191917</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U26" t="n">
-        <v>79.19191919191917</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V26" t="n">
-        <v>79.19191919191917</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W26" t="n">
-        <v>38.78787878787876</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X26" t="n">
-        <v>38.78787878787876</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="Y26" t="n">
-        <v>38.78787878787876</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="C27" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D27" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K27" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L27" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M27" t="n">
-        <v>42.8</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="N27" t="n">
-        <v>42.8</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O27" t="n">
-        <v>80.80000000000001</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P27" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S27" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T27" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U27" t="n">
-        <v>79.19191919191917</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V27" t="n">
-        <v>43.60404040404041</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W27" t="n">
-        <v>3.2</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.2</v>
+        <v>87.37278572049297</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="C28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="D28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="E28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="F28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="G28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="H28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="I28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="J28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="K28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="L28" t="n">
-        <v>56.87268517287855</v>
+        <v>69.3105240343566</v>
       </c>
       <c r="M28" t="n">
-        <v>96.06072336510073</v>
+        <v>108.4985622265788</v>
       </c>
       <c r="N28" t="n">
-        <v>135.6607233651007</v>
+        <v>152.1894128820151</v>
       </c>
       <c r="O28" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P28" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q28" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="R28" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="S28" t="n">
-        <v>160</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="T28" t="n">
-        <v>160</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="U28" t="n">
-        <v>150.7706813772868</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="V28" t="n">
-        <v>110.3666409732464</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="W28" t="n">
-        <v>69.96260056920597</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="X28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
       <c r="Y28" t="n">
-        <v>29.55856016516557</v>
+        <v>41.99639902664363</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>119.5959595959596</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="C29" t="n">
-        <v>119.5959595959596</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="D29" t="n">
-        <v>119.5959595959596</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E29" t="n">
-        <v>84.00808080808082</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="F29" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G29" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K29" t="n">
-        <v>42.8</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="L29" t="n">
-        <v>82.40000000000001</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="M29" t="n">
-        <v>82.40000000000001</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="N29" t="n">
-        <v>122</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="O29" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P29" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q29" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R29" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S29" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="T29" t="n">
-        <v>160</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="U29" t="n">
-        <v>119.5959595959596</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="V29" t="n">
-        <v>119.5959595959596</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="W29" t="n">
-        <v>119.5959595959596</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X29" t="n">
-        <v>119.5959595959596</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y29" t="n">
-        <v>119.5959595959596</v>
+        <v>48.10852568854899</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="C30" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="D30" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K30" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L30" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M30" t="n">
-        <v>41.20000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="N30" t="n">
-        <v>41.20000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="O30" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="P30" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R30" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S30" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T30" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="U30" t="n">
-        <v>79.19191919191917</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="V30" t="n">
-        <v>79.19191919191917</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="W30" t="n">
-        <v>79.19191919191917</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="X30" t="n">
-        <v>38.78787878787876</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="Y30" t="n">
-        <v>38.78787878787876</v>
+        <v>42.79483382228227</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C31" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D31" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E31" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F31" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G31" t="n">
-        <v>84.00808080808082</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H31" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L31" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M31" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N31" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P31" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q31" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R31" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S31" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T31" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U31" t="n">
-        <v>93.23739943079403</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="V31" t="n">
-        <v>93.23739943079403</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="W31" t="n">
-        <v>93.23739943079403</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="X31" t="n">
-        <v>93.23739943079403</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="Y31" t="n">
-        <v>93.23739943079403</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="C32" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D32" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="E32" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F32" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="H32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K32" t="n">
-        <v>42.8</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L32" t="n">
-        <v>80.80000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M32" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N32" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O32" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P32" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q32" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R32" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S32" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="T32" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="U32" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="V32" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="W32" t="n">
-        <v>119.5959595959596</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X32" t="n">
-        <v>119.5959595959596</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="Y32" t="n">
-        <v>79.19191919191917</v>
+        <v>87.37278572049297</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>84.00808080808082</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="C33" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="D33" t="n">
-        <v>43.60404040404041</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="E33" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="F33" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="G33" t="n">
-        <v>43.60404040404041</v>
+        <v>42.79483382228227</v>
       </c>
       <c r="H33" t="n">
-        <v>43.60404040404041</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K33" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L33" t="n">
-        <v>42.8</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M33" t="n">
-        <v>42.8</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="N33" t="n">
-        <v>80.80000000000001</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O33" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="P33" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q33" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R33" t="n">
-        <v>160</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="S33" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="T33" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="U33" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="V33" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="W33" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="X33" t="n">
-        <v>160</v>
+        <v>87.37278572049297</v>
       </c>
       <c r="Y33" t="n">
-        <v>119.5959595959596</v>
+        <v>87.37278572049297</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29.55856016516557</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="C34" t="n">
-        <v>29.55856016516557</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="D34" t="n">
-        <v>29.55856016516557</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="E34" t="n">
-        <v>29.55856016516557</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="F34" t="n">
-        <v>29.55856016516557</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="G34" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H34" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I34" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J34" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K34" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L34" t="n">
-        <v>56.87268517287855</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M34" t="n">
-        <v>96.06072336510073</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N34" t="n">
-        <v>135.6607233651007</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O34" t="n">
-        <v>160</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P34" t="n">
-        <v>157.2510699645389</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q34" t="n">
-        <v>116.8470295604985</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R34" t="n">
-        <v>76.44298915645805</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S34" t="n">
-        <v>36.03894875241765</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="T34" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="U34" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="V34" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="W34" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="X34" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="Y34" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C35" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="D35" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="E35" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="F35" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="G35" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K35" t="n">
-        <v>41.20000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L35" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="M35" t="n">
-        <v>80.80000000000001</v>
+        <v>134.6031257566472</v>
       </c>
       <c r="N35" t="n">
-        <v>80.80000000000001</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="O35" t="n">
-        <v>120.4</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T35" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U35" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V35" t="n">
-        <v>79.19191919191917</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W35" t="n">
-        <v>38.78787878787876</v>
+        <v>131.9507376187037</v>
       </c>
       <c r="X35" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.2</v>
+        <v>92.68647758675968</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K36" t="n">
-        <v>3.2</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="L36" t="n">
-        <v>42.8</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M36" t="n">
-        <v>82.40000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="N36" t="n">
-        <v>120.4</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="O36" t="n">
-        <v>120.4</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="P36" t="n">
-        <v>160</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="Q36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T36" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U36" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V36" t="n">
-        <v>79.19191919191917</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="W36" t="n">
-        <v>38.78787878787876</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="X36" t="n">
-        <v>38.78787878787876</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29.55856016516557</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="C37" t="n">
-        <v>29.55856016516557</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="D37" t="n">
-        <v>29.55856016516557</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="E37" t="n">
-        <v>29.55856016516557</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="F37" t="n">
-        <v>29.55856016516557</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="G37" t="n">
-        <v>29.55856016516557</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="H37" t="n">
-        <v>29.55856016516557</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="I37" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J37" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K37" t="n">
-        <v>29.55856016516557</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L37" t="n">
-        <v>56.87268517287855</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M37" t="n">
-        <v>96.06072336510073</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N37" t="n">
-        <v>135.6607233651007</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O37" t="n">
-        <v>160</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P37" t="n">
-        <v>160</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q37" t="n">
-        <v>160</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R37" t="n">
-        <v>160</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S37" t="n">
-        <v>119.5959595959596</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T37" t="n">
-        <v>119.5959595959596</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U37" t="n">
-        <v>119.5959595959596</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V37" t="n">
-        <v>119.5959595959596</v>
+        <v>138.062864280609</v>
       </c>
       <c r="W37" t="n">
-        <v>110.3666409732464</v>
+        <v>138.062864280609</v>
       </c>
       <c r="X37" t="n">
-        <v>69.96260056920597</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Y37" t="n">
-        <v>29.55856016516557</v>
+        <v>138.062864280609</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>43.60404040404041</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="C38" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="D38" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="E38" t="n">
-        <v>43.60404040404041</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K38" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L38" t="n">
-        <v>41.20000000000001</v>
+        <v>47.22142444577459</v>
       </c>
       <c r="M38" t="n">
-        <v>80.80000000000001</v>
+        <v>90.91227510121089</v>
       </c>
       <c r="N38" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R38" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S38" t="n">
-        <v>124.4121212121212</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T38" t="n">
-        <v>84.00808080808082</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U38" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="V38" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="W38" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="X38" t="n">
-        <v>43.60404040404041</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Y38" t="n">
-        <v>43.60404040404041</v>
+        <v>137.2644294849704</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="C39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="D39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="E39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="F39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="G39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="H39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="I39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="J39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K39" t="n">
-        <v>42.8</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L39" t="n">
-        <v>42.8</v>
+        <v>45.45613755060546</v>
       </c>
       <c r="M39" t="n">
-        <v>80.80000000000001</v>
+        <v>89.14698820604177</v>
       </c>
       <c r="N39" t="n">
-        <v>120.4</v>
+        <v>132.8378388614781</v>
       </c>
       <c r="O39" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="P39" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="Q39" t="n">
-        <v>160</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="R39" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="S39" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="T39" t="n">
-        <v>119.5959595959596</v>
+        <v>176.5286895169144</v>
       </c>
       <c r="U39" t="n">
-        <v>79.19191919191917</v>
+        <v>137.2644294849704</v>
       </c>
       <c r="V39" t="n">
-        <v>38.78787878787876</v>
+        <v>92.68647758675968</v>
       </c>
       <c r="W39" t="n">
-        <v>3.2</v>
+        <v>48.10852568854899</v>
       </c>
       <c r="X39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="C40" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="D40" t="n">
-        <v>52.83335902675362</v>
+        <v>138.062864280609</v>
       </c>
       <c r="E40" t="n">
-        <v>12.42931862271321</v>
+        <v>138.062864280609</v>
       </c>
       <c r="F40" t="n">
-        <v>3.2</v>
+        <v>138.062864280609</v>
       </c>
       <c r="G40" t="n">
-        <v>3.2</v>
+        <v>93.48491238239833</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>48.90696048418764</v>
       </c>
       <c r="I40" t="n">
-        <v>3.2</v>
+        <v>4.329008585976936</v>
       </c>
       <c r="J40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>3.530573790338288</v>
       </c>
       <c r="L40" t="n">
-        <v>30.51412500771298</v>
+        <v>30.84469879805127</v>
       </c>
       <c r="M40" t="n">
-        <v>69.70216319993516</v>
+        <v>70.03273699027345</v>
       </c>
       <c r="N40" t="n">
-        <v>109.3021631999352</v>
+        <v>113.7235876457098</v>
       </c>
       <c r="O40" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="P40" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Q40" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="R40" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="S40" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="T40" t="n">
-        <v>133.6414398348344</v>
+        <v>138.062864280609</v>
       </c>
       <c r="U40" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="V40" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="W40" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="X40" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
       <c r="Y40" t="n">
-        <v>93.23739943079403</v>
+        <v>138.062864280609</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>38.78787878787876</v>
+        <v>28.29275017052741</v>
       </c>
       <c r="C41" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="D41" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="E41" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F41" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G41" t="n">
-        <v>38.78787878787876</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K41" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L41" t="n">
-        <v>41.20000000000001</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="M41" t="n">
-        <v>41.20000000000001</v>
+        <v>40.77139327069581</v>
       </c>
       <c r="N41" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="O41" t="n">
-        <v>120.4</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="P41" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="R41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="S41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="T41" t="n">
-        <v>160</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="U41" t="n">
-        <v>119.5959595959596</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="V41" t="n">
-        <v>79.19191919191917</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="W41" t="n">
-        <v>38.78787878787876</v>
+        <v>148.2438924791353</v>
       </c>
       <c r="X41" t="n">
-        <v>38.78787878787876</v>
+        <v>108.260178376266</v>
       </c>
       <c r="Y41" t="n">
-        <v>38.78787878787876</v>
+        <v>68.2764642733967</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>38.78787878787876</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="C42" t="n">
-        <v>3.2</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="D42" t="n">
-        <v>3.2</v>
+        <v>38.38436553875449</v>
       </c>
       <c r="E42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="F42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K42" t="n">
-        <v>41.20000000000001</v>
+        <v>42.35474834916943</v>
       </c>
       <c r="L42" t="n">
-        <v>80.80000000000001</v>
+        <v>79.95943146291799</v>
       </c>
       <c r="M42" t="n">
-        <v>80.80000000000001</v>
+        <v>119.1474696551402</v>
       </c>
       <c r="N42" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="O42" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="P42" t="n">
-        <v>120.4</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="Q42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="R42" t="n">
-        <v>160</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="S42" t="n">
-        <v>119.5959595959596</v>
+        <v>158.3355078473624</v>
       </c>
       <c r="T42" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="U42" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="V42" t="n">
-        <v>119.5959595959596</v>
+        <v>118.3517937444931</v>
       </c>
       <c r="W42" t="n">
-        <v>79.19191919191917</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="X42" t="n">
-        <v>79.19191919191917</v>
+        <v>78.36807964162378</v>
       </c>
       <c r="Y42" t="n">
-        <v>38.78787878787876</v>
+        <v>38.38436553875449</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12.42931862271321</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="C43" t="n">
-        <v>12.42931862271321</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="D43" t="n">
-        <v>12.42931862271321</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="E43" t="n">
-        <v>12.42931862271321</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="F43" t="n">
-        <v>12.42931862271321</v>
+        <v>43.15042425981653</v>
       </c>
       <c r="G43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="H43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="K43" t="n">
-        <v>3.2</v>
+        <v>3.166710156947247</v>
       </c>
       <c r="L43" t="n">
-        <v>30.51412500771298</v>
+        <v>30.48083516466022</v>
       </c>
       <c r="M43" t="n">
-        <v>69.70216319993516</v>
+        <v>69.6688733568824</v>
       </c>
       <c r="N43" t="n">
-        <v>109.3021631999352</v>
+        <v>108.8569115491046</v>
       </c>
       <c r="O43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="P43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="Q43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="R43" t="n">
-        <v>133.6414398348344</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="S43" t="n">
-        <v>93.23739943079403</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="T43" t="n">
-        <v>93.23739943079403</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="U43" t="n">
-        <v>52.83335902675362</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="V43" t="n">
-        <v>52.83335902675362</v>
+        <v>133.1961881840039</v>
       </c>
       <c r="W43" t="n">
-        <v>52.83335902675362</v>
+        <v>93.21247408113457</v>
       </c>
       <c r="X43" t="n">
-        <v>52.83335902675362</v>
+        <v>53.22875997826529</v>
       </c>
       <c r="Y43" t="n">
-        <v>12.42931862271321</v>
+        <v>53.22875997826529</v>
       </c>
     </row>
     <row r="44">
@@ -9144,7 +9144,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>220.0898510449805</v>
+        <v>224.4543769505549</v>
       </c>
       <c r="L17" t="n">
         <v>235.7664149699872</v>
@@ -9153,13 +9153,13 @@
         <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>233.9613590139789</v>
       </c>
       <c r="O17" t="n">
-        <v>230.0982114216867</v>
+        <v>234.6465068390747</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>235.7812911726575</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,10 +9223,10 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>142.389734391747</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>143.1026751972622</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -9235,13 +9235,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>146.9607703500188</v>
       </c>
       <c r="P18" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>144.5300695034095</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9305,16 +9305,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L19" t="n">
-        <v>134.8846762812383</v>
+        <v>139.2492021868126</v>
       </c>
       <c r="M19" t="n">
-        <v>138.9257839476051</v>
+        <v>143.4740793649931</v>
       </c>
       <c r="N19" t="n">
-        <v>127.6855444652332</v>
+        <v>132.2338398826212</v>
       </c>
       <c r="O19" t="n">
-        <v>138.4565384518428</v>
+        <v>143.0048338692308</v>
       </c>
       <c r="P19" t="n">
         <v>135.0065633140411</v>
@@ -9381,19 +9381,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>260.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L20" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M20" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N20" t="n">
-        <v>267.7969019804293</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O20" t="n">
-        <v>270.0982114216868</v>
+        <v>272.4472657249869</v>
       </c>
       <c r="P20" t="n">
         <v>231.2329957552695</v>
@@ -9460,22 +9460,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>177.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L21" t="n">
-        <v>178.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M21" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>169.7255504671717</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>142.5962444444444</v>
+        <v>184.9452987477446</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q21" t="n">
         <v>139.9817740860215</v>
@@ -9548,7 +9548,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N22" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O22" t="n">
         <v>163.0416663658825</v>
@@ -9618,19 +9618,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>220.0898510449805</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L23" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M23" t="n">
-        <v>268.7300716111112</v>
+        <v>272.6952875305729</v>
       </c>
       <c r="N23" t="n">
-        <v>269.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P23" t="n">
         <v>231.2329957552695</v>
@@ -9697,22 +9697,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>171.3417120833333</v>
+        <v>173.6907663866335</v>
       </c>
       <c r="O24" t="n">
-        <v>182.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P24" t="n">
-        <v>172.3582457981686</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q24" t="n">
         <v>139.9817740860215</v>
@@ -9785,7 +9785,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N25" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O25" t="n">
         <v>163.0416663658825</v>
@@ -9855,22 +9855,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>260.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L26" t="n">
-        <v>235.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N26" t="n">
-        <v>269.4130635965909</v>
+        <v>271.7621178998911</v>
       </c>
       <c r="O26" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P26" t="n">
-        <v>269.6168341391079</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L27" t="n">
-        <v>178.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M27" t="n">
-        <v>142.1340339220183</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>173.6907663866335</v>
       </c>
       <c r="O27" t="n">
-        <v>180.9800828282828</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10022,7 +10022,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N28" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O28" t="n">
         <v>163.0416663658825</v>
@@ -10092,22 +10092,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>260.0898510449805</v>
+        <v>262.4389053482807</v>
       </c>
       <c r="L29" t="n">
-        <v>275.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M29" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N29" t="n">
-        <v>269.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O29" t="n">
-        <v>268.4820498055251</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P29" t="n">
-        <v>231.2329957552695</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10174,22 +10174,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M30" t="n">
-        <v>180.5178723058567</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>182.5962444444444</v>
+        <v>184.9452987477446</v>
       </c>
       <c r="P30" t="n">
-        <v>173.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q30" t="n">
-        <v>179.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10259,7 +10259,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N31" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O31" t="n">
         <v>163.0416663658825</v>
@@ -10329,22 +10329,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>260.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>274.1502533538256</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M32" t="n">
-        <v>230.3462332272727</v>
+        <v>272.6952875305729</v>
       </c>
       <c r="N32" t="n">
-        <v>229.4130635965909</v>
+        <v>273.5452359758195</v>
       </c>
       <c r="O32" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P32" t="n">
-        <v>271.2329957552695</v>
+        <v>275.3651681344982</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L33" t="n">
-        <v>178.5543797798742</v>
+        <v>182.6865521591028</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220183</v>
+        <v>184.4830882253185</v>
       </c>
       <c r="N33" t="n">
-        <v>169.7255504671717</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>182.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
-        <v>173.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10496,7 +10496,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N34" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O34" t="n">
         <v>163.0416663658825</v>
@@ -10566,22 +10566,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>258.4736894288189</v>
+        <v>264.2220234242092</v>
       </c>
       <c r="L35" t="n">
-        <v>275.7664149699872</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M35" t="n">
-        <v>230.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635965909</v>
+        <v>271.7621178998911</v>
       </c>
       <c r="O35" t="n">
-        <v>270.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P35" t="n">
-        <v>271.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>181.9736113535876</v>
       </c>
       <c r="L36" t="n">
-        <v>178.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>182.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>169.7255504671717</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>142.5962444444444</v>
+        <v>184.9452987477446</v>
       </c>
       <c r="P36" t="n">
-        <v>173.9744074143302</v>
+        <v>178.1065797935588</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>184.1139464652501</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10733,7 +10733,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N37" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O37" t="n">
         <v>163.0416663658825</v>
@@ -10806,16 +10806,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L38" t="n">
-        <v>274.1502533538256</v>
+        <v>279.8985873492159</v>
       </c>
       <c r="M38" t="n">
-        <v>270.3462332272727</v>
+        <v>274.4784056065013</v>
       </c>
       <c r="N38" t="n">
-        <v>269.4130635965909</v>
+        <v>271.7621178998911</v>
       </c>
       <c r="O38" t="n">
-        <v>270.0982114216868</v>
+        <v>274.2303838009153</v>
       </c>
       <c r="P38" t="n">
         <v>231.2329957552695</v>
@@ -10882,19 +10882,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>177.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>138.5543797798742</v>
+        <v>180.9034340831744</v>
       </c>
       <c r="M39" t="n">
-        <v>180.5178723058567</v>
+        <v>186.2662063012469</v>
       </c>
       <c r="N39" t="n">
-        <v>171.3417120833333</v>
+        <v>175.4738844625619</v>
       </c>
       <c r="O39" t="n">
-        <v>182.5962444444444</v>
+        <v>186.728416823673</v>
       </c>
       <c r="P39" t="n">
         <v>133.9744074143302</v>
@@ -10970,7 +10970,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N40" t="n">
-        <v>167.6855444652332</v>
+        <v>171.8177168444618</v>
       </c>
       <c r="O40" t="n">
         <v>163.0416663658825</v>
@@ -11040,22 +11040,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>258.4736894288189</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>230.3462332272727</v>
+        <v>268.3307616249986</v>
       </c>
       <c r="N41" t="n">
-        <v>269.4130635965909</v>
+        <v>268.9969405584315</v>
       </c>
       <c r="O41" t="n">
-        <v>270.0982114216868</v>
+        <v>269.6820883835273</v>
       </c>
       <c r="P41" t="n">
-        <v>271.2329957552695</v>
+        <v>270.8168727171101</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,16 +11119,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>176.2252773581974</v>
+        <v>177.4253159361996</v>
       </c>
       <c r="L42" t="n">
-        <v>178.5543797798742</v>
+        <v>176.5389081776</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>181.7179108838589</v>
       </c>
       <c r="N42" t="n">
-        <v>171.3417120833333</v>
+        <v>170.9255890451739</v>
       </c>
       <c r="O42" t="n">
         <v>142.5962444444444</v>
@@ -11137,7 +11137,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>179.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11207,7 +11207,7 @@
         <v>178.5096609094456</v>
       </c>
       <c r="N43" t="n">
-        <v>167.6855444652332</v>
+        <v>167.2694214270738</v>
       </c>
       <c r="O43" t="n">
         <v>163.0416663658825</v>
@@ -23734,19 +23734,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>5.984560610909452</v>
       </c>
       <c r="R17" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
-        <v>209.0200695862453</v>
+        <v>204.4717741688573</v>
       </c>
       <c r="T17" t="n">
-        <v>223.0958495641314</v>
+        <v>218.5475541467434</v>
       </c>
       <c r="U17" t="n">
-        <v>251.3456529078365</v>
+        <v>246.7973574904485</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23780,19 +23780,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>145.0692123933839</v>
+        <v>140.5209169759959</v>
       </c>
       <c r="G18" t="n">
-        <v>137.3435171632106</v>
+        <v>132.7952217458226</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>107.6871488191085</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>86.13708557403758</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23892,10 +23892,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>86.16204325169439</v>
+        <v>81.61374783430638</v>
       </c>
       <c r="R19" t="n">
-        <v>177.2933913771695</v>
+        <v>172.7450959597815</v>
       </c>
       <c r="S19" t="n">
         <v>224.0165980369723</v>
@@ -23910,10 +23910,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>286.522998336591</v>
+        <v>281.974702919203</v>
       </c>
       <c r="X19" t="n">
-        <v>225.7096553890372</v>
+        <v>221.7035167854018</v>
       </c>
       <c r="Y19" t="n">
         <v>218.5846533520948</v>
@@ -23971,31 +23971,31 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>169.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>183.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
-        <v>292.5202584701349</v>
+        <v>283.6200860909063</v>
       </c>
       <c r="W20" t="n">
-        <v>349.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X20" t="n">
-        <v>369.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>357.3570204389738</v>
       </c>
     </row>
     <row r="21">
@@ -24005,16 +24005,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>122.4010112706387</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>128.5763266090871</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>117.6450804554009</v>
+        <v>118.7734630237764</v>
       </c>
       <c r="F21" t="n">
         <v>145.0692123933839</v>
@@ -24053,13 +24053,13 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>60.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>136.4511711038379</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>160.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
         <v>225.9413820809748</v>
@@ -24074,7 +24074,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="22">
@@ -24087,7 +24087,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C22" t="n">
-        <v>127.2468210986278</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
@@ -24102,10 +24102,10 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H22" t="n">
-        <v>153.0901470709535</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I22" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J22" t="n">
         <v>93.35918011667277</v>
@@ -24135,22 +24135,22 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>224.0165980369723</v>
+        <v>179.8844256577437</v>
       </c>
       <c r="T22" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3190293564909</v>
+        <v>242.1868569772623</v>
       </c>
       <c r="V22" t="n">
-        <v>252.137643323828</v>
+        <v>208.0054709445994</v>
       </c>
       <c r="W22" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
-        <v>225.7096553890372</v>
+        <v>224.9192049413549</v>
       </c>
       <c r="Y22" t="n">
         <v>218.5846533520948</v>
@@ -24166,16 +24166,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>365.2728917710076</v>
+        <v>326.401274339383</v>
       </c>
       <c r="D23" t="n">
-        <v>314.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>371.6440457417115</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
         <v>415.302737515135</v>
@@ -24211,10 +24211,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>109.8691179411497</v>
+        <v>105.7369455619211</v>
       </c>
       <c r="S23" t="n">
-        <v>169.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
         <v>223.0958495641314</v>
@@ -24226,10 +24226,10 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y23" t="n">
         <v>386.2379386560536</v>
@@ -24290,25 +24290,25 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>56.02566177341454</v>
       </c>
       <c r="S24" t="n">
-        <v>136.4511711038379</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>160.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>185.9413820809748</v>
+        <v>187.0697646493503</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>188.6684147701967</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X24" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -24321,7 +24321,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>170.6949547454512</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C25" t="n">
         <v>167.2468210986278</v>
@@ -24333,13 +24333,13 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F25" t="n">
-        <v>145.4210480229312</v>
+        <v>101.2888756437027</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9909793584588</v>
+        <v>123.8588069792302</v>
       </c>
       <c r="H25" t="n">
-        <v>162.2271725074396</v>
+        <v>161.4367220597573</v>
       </c>
       <c r="I25" t="n">
         <v>155.4504749272583</v>
@@ -24366,10 +24366,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S25" t="n">
         <v>224.0165980369723</v>
@@ -24384,10 +24384,10 @@
         <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>286.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X25" t="n">
-        <v>185.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y25" t="n">
         <v>218.5846533520948</v>
@@ -24421,7 +24421,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
-        <v>175.2438895704059</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -24448,10 +24448,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>109.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>169.0200695862453</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
         <v>223.0958495641314</v>
@@ -24460,16 +24460,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>283.6200860909063</v>
       </c>
       <c r="W26" t="n">
-        <v>309.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X26" t="n">
-        <v>369.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>347.366321224429</v>
       </c>
     </row>
     <row r="27">
@@ -24485,10 +24485,10 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>108.5734481330142</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>113.5129080761724</v>
       </c>
       <c r="F27" t="n">
         <v>145.0692123933839</v>
@@ -24533,22 +24533,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>160.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>197.5685871494253</v>
+        <v>188.6684147701967</v>
       </c>
       <c r="W27" t="n">
-        <v>211.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>205.6826957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="28">
@@ -24603,28 +24603,28 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q28" t="n">
-        <v>86.16204325169439</v>
+        <v>42.02987087246579</v>
       </c>
       <c r="R28" t="n">
-        <v>177.2933913771695</v>
+        <v>133.1612189979409</v>
       </c>
       <c r="S28" t="n">
-        <v>224.0165980369723</v>
+        <v>179.8844256577437</v>
       </c>
       <c r="T28" t="n">
-        <v>227.9455894282815</v>
+        <v>227.1551389805992</v>
       </c>
       <c r="U28" t="n">
-        <v>277.1820039200048</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
-        <v>212.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>246.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
-        <v>185.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y28" t="n">
         <v>218.5846533520948</v>
@@ -24646,16 +24646,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>346.6983700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>366.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>415.302737515135</v>
+        <v>371.1705651359065</v>
       </c>
       <c r="H29" t="n">
-        <v>299.4748021157671</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
@@ -24688,22 +24688,22 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>170.1484521546208</v>
       </c>
       <c r="T29" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>283.6200860909063</v>
       </c>
       <c r="W29" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y29" t="n">
         <v>386.2379386560536</v>
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>131.3011836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
         <v>172.7084989883157</v>
@@ -24725,7 +24725,7 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>118.7734630237764</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
@@ -24767,13 +24767,13 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>131.6831711038378</v>
+        <v>127.5509987246092</v>
       </c>
       <c r="T30" t="n">
-        <v>160.1647286948216</v>
+        <v>156.032556315593</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>181.8092097017462</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24782,7 +24782,7 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X30" t="n">
-        <v>165.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
         <v>205.6826957773044</v>
@@ -24807,16 +24807,16 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F31" t="n">
-        <v>136.2840225864452</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
         <v>167.9909793584588</v>
       </c>
       <c r="H31" t="n">
-        <v>122.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I31" t="n">
-        <v>115.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -24840,7 +24840,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>46.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
         <v>177.2933913771695</v>
@@ -24852,19 +24852,19 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3190293564909</v>
+        <v>242.1868569772623</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W31" t="n">
-        <v>286.522998336591</v>
+        <v>242.3908259573624</v>
       </c>
       <c r="X31" t="n">
-        <v>225.7096553890372</v>
+        <v>181.5774830098086</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>217.7942029044125</v>
       </c>
     </row>
     <row r="32">
@@ -24877,10 +24877,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>330.0408917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>314.683041620683</v>
+        <v>310.5508692414544</v>
       </c>
       <c r="E32" t="n">
         <v>381.9303700722618</v>
@@ -24892,7 +24892,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
-        <v>339.4748021157671</v>
+        <v>300.6031846841426</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
@@ -24922,7 +24922,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>109.8691179411497</v>
+        <v>105.7369455619211</v>
       </c>
       <c r="S32" t="n">
         <v>209.0200695862453</v>
@@ -24940,10 +24940,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>369.731100678469</v>
+        <v>325.5989282992405</v>
       </c>
       <c r="Y32" t="n">
-        <v>346.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24953,16 +24953,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>131.3011836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>132.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
-        <v>157.6450804554009</v>
+        <v>113.5129080761724</v>
       </c>
       <c r="F33" t="n">
         <v>145.0692123933839</v>
@@ -24971,10 +24971,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>73.36382680487192</v>
       </c>
       <c r="I33" t="n">
-        <v>49.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
         <v>0.7465913262578567</v>
@@ -25001,10 +25001,10 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>56.02566177341454</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>127.5509987246092</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
@@ -25022,7 +25022,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>165.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25032,7 +25032,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>179.8319801819373</v>
+        <v>135.6998078027087</v>
       </c>
       <c r="C34" t="n">
         <v>167.2468210986278</v>
@@ -25044,10 +25044,10 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F34" t="n">
-        <v>145.4210480229312</v>
+        <v>101.2888756437027</v>
       </c>
       <c r="G34" t="n">
-        <v>167.9909793584588</v>
+        <v>167.2005289107765</v>
       </c>
       <c r="H34" t="n">
         <v>162.2271725074396</v>
@@ -25074,19 +25074,19 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>46.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>137.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
-        <v>184.0165980369723</v>
+        <v>179.8844256577437</v>
       </c>
       <c r="T34" t="n">
-        <v>221.530004726902</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U34" t="n">
         <v>286.3190293564909</v>
@@ -25120,7 +25120,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E35" t="n">
-        <v>381.9303700722618</v>
+        <v>337.7981976930332</v>
       </c>
       <c r="F35" t="n">
         <v>406.8760457417114</v>
@@ -25129,7 +25129,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>295.3426297365386</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25168,16 +25168,16 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>309.240968717413</v>
+        <v>305.1087963381844</v>
       </c>
       <c r="X35" t="n">
-        <v>334.4991006784691</v>
+        <v>330.8594832468445</v>
       </c>
       <c r="Y35" t="n">
         <v>386.2379386560536</v>
@@ -25247,19 +25247,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>185.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>192.8005871494253</v>
+        <v>193.9289697178007</v>
       </c>
       <c r="W36" t="n">
-        <v>211.6949831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>161.6408128242489</v>
       </c>
       <c r="Y36" t="n">
-        <v>170.4506957773044</v>
+        <v>161.5505233980758</v>
       </c>
     </row>
     <row r="37">
@@ -25269,10 +25269,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>179.8319801819373</v>
+        <v>135.6998078027087</v>
       </c>
       <c r="C37" t="n">
-        <v>167.2468210986278</v>
+        <v>123.1146487193992</v>
       </c>
       <c r="D37" t="n">
         <v>148.6154730182124</v>
@@ -25284,13 +25284,13 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.9909793584588</v>
+        <v>123.8588069792302</v>
       </c>
       <c r="H37" t="n">
         <v>162.2271725074396</v>
       </c>
       <c r="I37" t="n">
-        <v>155.4504749272583</v>
+        <v>154.660024479576</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -25320,7 +25320,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
-        <v>184.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
         <v>227.9455894282815</v>
@@ -25332,13 +25332,13 @@
         <v>252.137643323828</v>
       </c>
       <c r="W37" t="n">
-        <v>277.3859729001049</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X37" t="n">
-        <v>185.7096553890372</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y37" t="n">
-        <v>178.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="38">
@@ -25348,10 +25348,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>382.7338416634806</v>
+        <v>338.601669284252</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>321.1407193917789</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
@@ -25360,7 +25360,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>366.8760457417114</v>
+        <v>362.7438733624829</v>
       </c>
       <c r="G38" t="n">
         <v>415.302737515135</v>
@@ -25399,13 +25399,13 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
-        <v>173.7880695862454</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>183.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>347.366321224429</v>
       </c>
     </row>
     <row r="39">
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>60.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
@@ -25484,16 +25484,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>185.9413820809748</v>
+        <v>187.0697646493503</v>
       </c>
       <c r="V39" t="n">
-        <v>192.8005871494253</v>
+        <v>188.6684147701967</v>
       </c>
       <c r="W39" t="n">
-        <v>216.4629831609196</v>
+        <v>207.562810781691</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>161.6408128242489</v>
       </c>
       <c r="Y39" t="n">
         <v>205.6826957773044</v>
@@ -25512,25 +25512,25 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D40" t="n">
-        <v>108.6154730182124</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E40" t="n">
-        <v>106.4339626465692</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F40" t="n">
-        <v>136.2840225864452</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.9909793584588</v>
+        <v>123.8588069792302</v>
       </c>
       <c r="H40" t="n">
-        <v>162.2271725074396</v>
+        <v>118.095000128211</v>
       </c>
       <c r="I40" t="n">
-        <v>155.4504749272583</v>
+        <v>111.3183025480297</v>
       </c>
       <c r="J40" t="n">
-        <v>93.35918011667277</v>
+        <v>92.56872966899051</v>
       </c>
       <c r="K40" t="n">
         <v>22.26949182588285</v>
@@ -25563,7 +25563,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25585,10 +25585,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>343.14996470164</v>
       </c>
       <c r="C41" t="n">
-        <v>365.2728917710076</v>
+        <v>340.3981121575632</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25603,7 +25603,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>304.2428021157672</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25642,19 +25642,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>211.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>287.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>309.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>369.731100678469</v>
+        <v>330.1472237166284</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>346.654061694213</v>
       </c>
     </row>
     <row r="42">
@@ -25667,13 +25667,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>137.4764989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>122.7796016274118</v>
       </c>
       <c r="F42" t="n">
         <v>145.0692123933839</v>
@@ -25715,10 +25715,10 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>131.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>160.580851732981</v>
       </c>
       <c r="U42" t="n">
         <v>225.9413820809748</v>
@@ -25727,13 +25727,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>211.6949831609196</v>
+        <v>212.111106199079</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>165.6826957773044</v>
+        <v>166.0988188154638</v>
       </c>
     </row>
     <row r="43">
@@ -25755,10 +25755,10 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F43" t="n">
-        <v>145.4210480229312</v>
+        <v>135.443495661667</v>
       </c>
       <c r="G43" t="n">
-        <v>158.8539539219727</v>
+        <v>128.4071023966182</v>
       </c>
       <c r="H43" t="n">
         <v>162.2271725074396</v>
@@ -25794,25 +25794,25 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S43" t="n">
-        <v>184.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>246.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
-        <v>286.522998336591</v>
+        <v>246.9391213747504</v>
       </c>
       <c r="X43" t="n">
-        <v>225.7096553890372</v>
+        <v>186.1257784271966</v>
       </c>
       <c r="Y43" t="n">
-        <v>178.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="44">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333272.9571474838</v>
+        <v>337270.0002996555</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355498</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355498</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355497</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355498</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>367453.5983135024</v>
+        <v>370638.7740355498</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>367453.5983135026</v>
+        <v>370638.7740355498</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>367453.5983135027</v>
+        <v>367132.8408820864</v>
       </c>
     </row>
     <row r="16">
@@ -26264,43 +26264,43 @@
         <v>53753.7027657232</v>
       </c>
       <c r="C2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="D2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="E2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="F2" t="n">
-        <v>53753.70276572321</v>
+        <v>53753.7027657232</v>
       </c>
       <c r="G2" t="n">
-        <v>53753.70276572321</v>
+        <v>54397.96517295989</v>
       </c>
       <c r="H2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559937</v>
       </c>
       <c r="I2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559938</v>
       </c>
       <c r="J2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559938</v>
       </c>
       <c r="K2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559937</v>
       </c>
       <c r="L2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559938</v>
       </c>
       <c r="M2" t="n">
-        <v>59263.10091834211</v>
+        <v>59776.50267559939</v>
       </c>
       <c r="N2" t="n">
-        <v>59263.10091834213</v>
+        <v>59776.50267559939</v>
       </c>
       <c r="O2" t="n">
-        <v>59263.10091834212</v>
+        <v>59211.39971146602</v>
       </c>
       <c r="P2" t="n">
         <v>53753.70276572321</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1246.619549474791</v>
       </c>
       <c r="H3" t="n">
-        <v>10792.36</v>
+        <v>10680.08625919725</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10750.74055314464</v>
+        <v>8660.46003841522</v>
       </c>
       <c r="C4" t="n">
-        <v>10750.74055314464</v>
+        <v>8660.46003841522</v>
       </c>
       <c r="D4" t="n">
-        <v>10750.74055314464</v>
+        <v>8660.46003841522</v>
       </c>
       <c r="E4" t="n">
-        <v>10750.74055314464</v>
+        <v>8660.46003841522</v>
       </c>
       <c r="F4" t="n">
-        <v>10750.74055314464</v>
+        <v>8660.46003841522</v>
       </c>
       <c r="G4" t="n">
-        <v>10750.74055314464</v>
+        <v>8770.311175829025</v>
       </c>
       <c r="H4" t="n">
-        <v>11908.72037095864</v>
+        <v>9687.388527621028</v>
       </c>
       <c r="I4" t="n">
-        <v>11908.72037095864</v>
+        <v>9687.388527621029</v>
       </c>
       <c r="J4" t="n">
-        <v>11908.72037095864</v>
+        <v>9687.388527621028</v>
       </c>
       <c r="K4" t="n">
-        <v>11908.72037095864</v>
+        <v>9687.388527621028</v>
       </c>
       <c r="L4" t="n">
-        <v>11908.72037095864</v>
+        <v>9687.388527621029</v>
       </c>
       <c r="M4" t="n">
-        <v>11908.72037095864</v>
+        <v>9687.388527621028</v>
       </c>
       <c r="N4" t="n">
-        <v>11908.72037095864</v>
+        <v>9687.388527621028</v>
       </c>
       <c r="O4" t="n">
-        <v>11908.72037095864</v>
+        <v>9591.0346155059</v>
       </c>
       <c r="P4" t="n">
-        <v>10750.74055314464</v>
+        <v>8660.46003841522</v>
       </c>
     </row>
     <row r="5">
@@ -26432,31 +26432,31 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>276.5363613771906</v>
       </c>
       <c r="H5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="I5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="J5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="K5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="L5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="M5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="N5" t="n">
-        <v>2432</v>
+        <v>2683.236080657098</v>
       </c>
       <c r="O5" t="n">
-        <v>2432</v>
+        <v>2406.699719279908</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9375.362212578562</v>
+        <v>11465.64272730798</v>
       </c>
       <c r="C6" t="n">
-        <v>9375.36221257857</v>
+        <v>11465.64272730798</v>
       </c>
       <c r="D6" t="n">
-        <v>9375.36221257857</v>
+        <v>11465.64272730798</v>
       </c>
       <c r="E6" t="n">
-        <v>43002.96221257857</v>
+        <v>45093.24272730798</v>
       </c>
       <c r="F6" t="n">
-        <v>43002.96221257857</v>
+        <v>45093.24272730798</v>
       </c>
       <c r="G6" t="n">
-        <v>43002.96221257857</v>
+        <v>44104.49808627889</v>
       </c>
       <c r="H6" t="n">
-        <v>34130.02054738349</v>
+        <v>36725.791808124</v>
       </c>
       <c r="I6" t="n">
-        <v>44922.38054738349</v>
+        <v>47405.87806732125</v>
       </c>
       <c r="J6" t="n">
-        <v>44922.38054738349</v>
+        <v>47405.87806732125</v>
       </c>
       <c r="K6" t="n">
-        <v>44922.38054738349</v>
+        <v>47405.87806732124</v>
       </c>
       <c r="L6" t="n">
-        <v>44922.38054738349</v>
+        <v>47405.87806732125</v>
       </c>
       <c r="M6" t="n">
-        <v>44922.38054738348</v>
+        <v>47405.87806732126</v>
       </c>
       <c r="N6" t="n">
-        <v>44922.38054738349</v>
+        <v>47405.87806732126</v>
       </c>
       <c r="O6" t="n">
-        <v>44922.38054738348</v>
+        <v>47213.6653766802</v>
       </c>
       <c r="P6" t="n">
-        <v>43002.96221257857</v>
+        <v>45093.24272730799</v>
       </c>
     </row>
   </sheetData>
@@ -26742,31 +26742,31 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="I4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="J4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26959,10 +26959,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P4" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
     </row>
   </sheetData>
@@ -35799,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -35808,13 +35808,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,10 +35878,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -35890,13 +35890,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35960,16 +35960,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>4.36452590557435</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.548295417388005</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -36036,19 +36036,19 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O20" t="n">
-        <v>40</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36115,22 +36115,22 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L21" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36203,7 +36203,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N22" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O22" t="n">
         <v>24.58512791403967</v>
@@ -36273,19 +36273,19 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M23" t="n">
-        <v>38.38383838383839</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36352,22 +36352,22 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="O24" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P24" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36440,7 +36440,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N25" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O25" t="n">
         <v>24.58512791403967</v>
@@ -36510,22 +36510,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N26" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="O26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="O27" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36677,7 +36677,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O28" t="n">
         <v>24.58512791403967</v>
@@ -36747,22 +36747,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O29" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36829,22 +36829,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M30" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>40</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="P30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36914,7 +36914,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O31" t="n">
         <v>24.58512791403967</v>
@@ -36984,22 +36984,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="N33" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37151,7 +37151,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N34" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O34" t="n">
         <v>24.58512791403967</v>
@@ -37221,22 +37221,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>42.34905430330016</v>
       </c>
       <c r="O35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="P36" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37388,7 +37388,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O37" t="n">
         <v>24.58512791403967</v>
@@ -37461,16 +37461,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="M38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N38" t="n">
-        <v>40</v>
+        <v>42.34905430330019</v>
       </c>
       <c r="O38" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37537,19 +37537,19 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>42.34905430330018</v>
       </c>
       <c r="M39" t="n">
-        <v>38.38383838383839</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="N39" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O39" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -37625,7 +37625,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N40" t="n">
-        <v>40</v>
+        <v>44.13217237922859</v>
       </c>
       <c r="O40" t="n">
         <v>24.58512791403967</v>
@@ -37695,22 +37695,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>38.38383838383839</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="N41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="P41" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,16 +37774,16 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>38.38383838383839</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="L42" t="n">
-        <v>40</v>
+        <v>37.98452839772582</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="N42" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -37792,7 +37792,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37862,7 +37862,7 @@
         <v>39.58387696184059</v>
       </c>
       <c r="N43" t="n">
-        <v>40</v>
+        <v>39.58387696184059</v>
       </c>
       <c r="O43" t="n">
         <v>24.58512791403967</v>
